--- a/docs/detail-design/08_TaoSuaDon.xlsx
+++ b/docs/detail-design/08_TaoSuaDon.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="297">
   <si>
     <t>SWEET HOME · DETAIL DESIGN · TẠO / SỬA ĐƠN THUÊ</t>
   </si>
@@ -138,6 +138,12 @@
     <t>Tạo mới.</t>
   </si>
   <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Phòng còn khách Quá giờ / Chờ xác nhận trả coi là bận tới bây giờ + 1 tiếng (ảnh 3); ô bắt buộc thiếu tô đỏ + hộp lỗi khi lưu (ảnh 6); giới hạn độ dài ô chữ.</t>
+  </si>
+  <si>
     <t>Ảnh 1. Tạo đơn theo giờ, khách tự check-in</t>
   </si>
   <si>
@@ -147,16 +153,25 @@
     <t>Phòng đã có đơn trong khung giờ: báo lỗi đỏ, khoá nút lưu.</t>
   </si>
   <si>
-    <t>Ảnh 3. Thuê theo ngày, vượt số khách tối đa</t>
-  </si>
-  <si>
-    <t>Ảnh 4. Lưu đơn khách tự check-in khi chưa nhập mã cửa</t>
-  </si>
-  <si>
-    <t>Ảnh 5. Sửa đơn (Quản lý)</t>
-  </si>
-  <si>
-    <t>Ảnh 6. Sửa đơn (Nhân viên): không sửa được tiền cọc</t>
+    <t>Ảnh 3. Phòng còn khách quá giờ chưa trả</t>
+  </si>
+  <si>
+    <t>Phòng 102 có đơn Quá giờ: giờ hẹn trả đã qua nhưng phòng vẫn bận tới bây giờ + 1 tiếng.</t>
+  </si>
+  <si>
+    <t>Ảnh 4. Thuê theo ngày, vượt số khách tối đa</t>
+  </si>
+  <si>
+    <t>Ảnh 5. Lưu đơn khách tự check-in khi chưa nhập mã cửa</t>
+  </si>
+  <si>
+    <t>Ảnh 6. Lưu đơn khi chưa nhập họ tên, số điện thoại</t>
+  </si>
+  <si>
+    <t>Ảnh 7. Sửa đơn (Quản lý)</t>
+  </si>
+  <si>
+    <t>Ảnh 8. Sửa đơn (Nhân viên): không sửa được tiền cọc</t>
   </si>
   <si>
     <t>STT</t>
@@ -324,7 +339,7 @@
     <t>preview().available · conflictMessage</t>
   </si>
   <si>
-    <t>Xanh "Phòng trống trong khung giờ này." / đỏ "Phòng đã có đơn {mã} trong khung giờ này" (ảnh 2).</t>
+    <t>Xanh "Phòng trống trong khung giờ này." / đỏ "Phòng đã có đơn {mã} trong khung giờ này" (ảnh 2) hoặc "Phòng còn khách đơn {mã} chưa trả phòng" (ảnh 3).</t>
   </si>
   <si>
     <t>Nhận &amp; trả phòng</t>
@@ -357,7 +372,7 @@
     <t>Có (khách tự check-in)</t>
   </si>
   <si>
-    <t>Lưu mã hoá AES. Sửa đơn: để trống = giữ mã cũ (placeholder "Để trống để giữ mã cũ").</t>
+    <t>Tối đa 20 ký tự. Lưu mã hoá AES. Sửa đơn: để trống = giữ mã cũ (placeholder "Để trống để giữ mã cũ").</t>
   </si>
   <si>
     <t>(trống)</t>
@@ -375,7 +390,7 @@
     <t>form.controls.guestPhone</t>
   </si>
   <si>
-    <t>Không để trống (backend tối đa 20 ký tự theo cột DB).</t>
+    <t>Không để trống. Tối đa 20 ký tự.</t>
   </si>
   <si>
     <t>Họ tên</t>
@@ -387,7 +402,7 @@
     <t>form.controls.guestName</t>
   </si>
   <si>
-    <t>Không để trống.</t>
+    <t>Không để trống. Tối đa 100 ký tự.</t>
   </si>
   <si>
     <t>CCCD / Hộ chiếu</t>
@@ -402,7 +417,7 @@
     <t>Không</t>
   </si>
   <si>
-    <t>Bỏ khoảng trắng rồi mã hoá AES; lưu thêm 4 ký tự cuối để hiển thị che. Sửa đơn: để trống = giữ.</t>
+    <t>Tối đa 20 ký tự. Bỏ khoảng trắng rồi mã hoá AES; lưu thêm 4 ký tự cuối để hiển thị che. Sửa đơn: để trống = giữ.</t>
   </si>
   <si>
     <t>Số khách</t>
@@ -582,6 +597,12 @@
     <t>"Phòng đã có đơn SH-xxxx trong khung giờ này" — kiểm tra theo chặng của các đơn chưa huỷ ở phòng đó.</t>
   </si>
   <si>
+    <t>Báo phòng còn khách</t>
+  </si>
+  <si>
+    <t>"Phòng còn khách đơn SH-xxxx chưa trả phòng": chặng hiện tại của đơn Quá giờ / Chờ xác nhận trả coi là kéo dài tới bây giờ + 1 tiếng. Đặt giờ nhận sau mốc đó thì vẫn trống.</t>
+  </si>
+  <si>
     <t>Số ngày thuê</t>
   </si>
   <si>
@@ -618,6 +639,27 @@
     <t>Lỗi frontend ("Phải nhập mã cửa khi khách tự check-in.") hoặc detail lỗi từ server khi lưu (xem sheet 4).</t>
   </si>
   <si>
+    <t>Hộp lỗi ô bắt buộc</t>
+  </si>
+  <si>
+    <t>rejectInvalid() (core/form-errors.ts)</t>
+  </si>
+  <si>
+    <t>"Vui lòng nhập đủ các ô bắt buộc (viền đỏ)." Không gửi request.</t>
+  </si>
+  <si>
+    <t>Ô bắt buộc chưa nhập</t>
+  </si>
+  <si>
+    <t>Ô nhập (viền đỏ)</t>
+  </si>
+  <si>
+    <t>.inp.ng-invalid.ng-touched (styles.scss)</t>
+  </si>
+  <si>
+    <t>Ô bắt buộc trống / không hợp lệ đã chạm (hoặc đã bấm Lưu) có viền đỏ (ở ảnh: Số điện thoại, Họ tên, Tiền cọc); bấm Lưu thì con trỏ nhảy tới ô lỗi đầu tiên.</t>
+  </si>
+  <si>
     <t>Tiêu đề Sửa đơn</t>
   </si>
   <si>
@@ -711,7 +753,7 @@
     <t>Ngày + giờ nhận → + số giờ (≥ số giờ tối thiểu)</t>
   </si>
   <si>
-    <t>Giá 2 giờ đầu + (số giờ − số giờ tối thiểu) × giá mỗi giờ thêm</t>
+    <t>Giá "{số giờ tối thiểu} giờ đầu" + (số giờ − số giờ tối thiểu) × giá mỗi giờ thêm</t>
   </si>
   <si>
     <t>Qua đêm</t>
@@ -738,7 +780,7 @@
     <t>3. Lưu</t>
   </si>
   <si>
-    <t>Frontend chặn: form thiếu ô bắt buộc (không tô đỏ ô, chỉ không gửi), lỗi tiền cọc, khách tự check-in mà chưa có mã cửa (tạo mới, hoặc sửa đơn chưa có mã) → hộp lỗi.</t>
+    <t>Frontend chặn: form thiếu ô bắt buộc → tô đỏ ô, hộp lỗi "Vui lòng nhập đủ các ô bắt buộc (viền đỏ)."; lỗi tiền cọc (dưới ô); khách tự check-in mà chưa có mã cửa (tạo mới, hoặc sửa đơn chưa có mã) → hộp lỗi.</t>
   </si>
   <si>
     <t>Tạo: POST /api/orders; Sửa: PUT /api/orders/{id}. Thành công → /don-thue?id={id} (Lưu &amp; sao chép: thêm action=copy).</t>
@@ -772,6 +814,27 @@
   </si>
   <si>
     <t>Phòng đã có đơn {mã} trong khung giờ này</t>
+  </si>
+  <si>
+    <t>Giờ nhận trước bây giờ + 1 tiếng, phòng còn khách Quá giờ / Chờ xác nhận trả</t>
+  </si>
+  <si>
+    <t>Phòng còn khách đơn {mã} chưa trả phòng</t>
+  </si>
+  <si>
+    <t>Thiếu ô bắt buộc</t>
+  </si>
+  <si>
+    <t>frontend</t>
+  </si>
+  <si>
+    <t>Vui lòng nhập đủ các ô bắt buộc (viền đỏ).</t>
+  </si>
+  <si>
+    <t>Ô chữ quá dài (gọi thẳng API)</t>
+  </si>
+  <si>
+    <t>Dữ liệu không hợp lệ — errors.{trường}: "Tối đa N ký tự"</t>
   </si>
   <si>
     <t>Tiền cọc vượt tổng</t>
@@ -1078,10 +1141,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9658350" cy="11261367"/>
+    <xdr:ext cx="9658350" cy="6036468"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Picture 3">
@@ -1117,10 +1180,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>160</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9658350" cy="6036468"/>
+    <xdr:ext cx="9658350" cy="11261367"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="4" name="Picture 4">
@@ -1156,10 +1219,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>195</xdr:row>
+      <xdr:row>196</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="9658350" cy="11261367"/>
+    <xdr:ext cx="9658350" cy="6036468"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="5" name="Picture 5">
@@ -1195,10 +1258,10 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>258</xdr:row>
+      <xdr:row>231</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7200900" cy="3076575"/>
+    <xdr:ext cx="9658350" cy="11274782"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="6" name="Picture 6">
@@ -1230,6 +1293,84 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>294</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="9658350" cy="11261367"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>357</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7200900" cy="3076575"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1239,7 +1380,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="6457950" cy="20821650"/>
@@ -1602,7 +1743,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG21"/>
+  <dimension ref="B1:AG22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2333,8 +2474,50 @@
       <c r="AF21" s="3"/>
       <c r="AG21" s="3"/>
     </row>
+    <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="3"/>
+      <c r="AD22" s="3"/>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="43">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="I2:AG2"/>
@@ -2374,6 +2557,10 @@
     <mergeCell ref="E21:H21"/>
     <mergeCell ref="I21:M21"/>
     <mergeCell ref="N21:AG21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="I22:M22"/>
+    <mergeCell ref="N22:AG22"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -2384,7 +2571,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG258"/>
+  <dimension ref="B1:AG357"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2393,7 +2580,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2429,7 +2616,7 @@
     </row>
     <row r="61" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B61" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C61" s="4"/>
       <c r="D61" s="4"/>
@@ -2465,7 +2652,7 @@
     </row>
     <row r="62" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B62" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="6"/>
@@ -2501,7 +2688,7 @@
     </row>
     <row r="97" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B97" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C97" s="4"/>
       <c r="D97" s="4"/>
@@ -2535,123 +2722,234 @@
       <c r="AF97" s="4"/>
       <c r="AG97" s="4"/>
     </row>
-    <row r="160" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B160" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
-      <c r="F160" s="4"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
-      <c r="K160" s="4"/>
-      <c r="L160" s="4"/>
-      <c r="M160" s="4"/>
-      <c r="N160" s="4"/>
-      <c r="O160" s="4"/>
-      <c r="P160" s="4"/>
-      <c r="Q160" s="4"/>
-      <c r="R160" s="4"/>
-      <c r="S160" s="4"/>
-      <c r="T160" s="4"/>
-      <c r="U160" s="4"/>
-      <c r="V160" s="4"/>
-      <c r="W160" s="4"/>
-      <c r="X160" s="4"/>
-      <c r="Y160" s="4"/>
-      <c r="Z160" s="4"/>
-      <c r="AA160" s="4"/>
-      <c r="AB160" s="4"/>
-      <c r="AC160" s="4"/>
-      <c r="AD160" s="4"/>
-      <c r="AE160" s="4"/>
-      <c r="AF160" s="4"/>
-      <c r="AG160" s="4"/>
-    </row>
-    <row r="195" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B195" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C195" s="4"/>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-      <c r="I195" s="4"/>
-      <c r="J195" s="4"/>
-      <c r="K195" s="4"/>
-      <c r="L195" s="4"/>
-      <c r="M195" s="4"/>
-      <c r="N195" s="4"/>
-      <c r="O195" s="4"/>
-      <c r="P195" s="4"/>
-      <c r="Q195" s="4"/>
-      <c r="R195" s="4"/>
-      <c r="S195" s="4"/>
-      <c r="T195" s="4"/>
-      <c r="U195" s="4"/>
-      <c r="V195" s="4"/>
-      <c r="W195" s="4"/>
-      <c r="X195" s="4"/>
-      <c r="Y195" s="4"/>
-      <c r="Z195" s="4"/>
-      <c r="AA195" s="4"/>
-      <c r="AB195" s="4"/>
-      <c r="AC195" s="4"/>
-      <c r="AD195" s="4"/>
-      <c r="AE195" s="4"/>
-      <c r="AF195" s="4"/>
-      <c r="AG195" s="4"/>
-    </row>
-    <row r="258" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B258" s="4" t="s">
+    <row r="98" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B98" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
-      <c r="H258" s="4"/>
-      <c r="I258" s="4"/>
-      <c r="J258" s="4"/>
-      <c r="K258" s="4"/>
-      <c r="L258" s="4"/>
-      <c r="M258" s="4"/>
-      <c r="N258" s="4"/>
-      <c r="O258" s="4"/>
-      <c r="P258" s="4"/>
-      <c r="Q258" s="4"/>
-      <c r="R258" s="4"/>
-      <c r="S258" s="4"/>
-      <c r="T258" s="4"/>
-      <c r="U258" s="4"/>
-      <c r="V258" s="4"/>
-      <c r="W258" s="4"/>
-      <c r="X258" s="4"/>
-      <c r="Y258" s="4"/>
-      <c r="Z258" s="4"/>
-      <c r="AA258" s="4"/>
-      <c r="AB258" s="4"/>
-      <c r="AC258" s="4"/>
-      <c r="AD258" s="4"/>
-      <c r="AE258" s="4"/>
-      <c r="AF258" s="4"/>
-      <c r="AG258" s="4"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
+      <c r="V98" s="6"/>
+      <c r="W98" s="6"/>
+      <c r="X98" s="6"/>
+      <c r="Y98" s="6"/>
+      <c r="Z98" s="6"/>
+      <c r="AA98" s="6"/>
+      <c r="AB98" s="6"/>
+      <c r="AC98" s="6"/>
+      <c r="AD98" s="6"/>
+      <c r="AE98" s="6"/>
+      <c r="AF98" s="6"/>
+      <c r="AG98" s="6"/>
+    </row>
+    <row r="133" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B133" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C133" s="4"/>
+      <c r="D133" s="4"/>
+      <c r="E133" s="4"/>
+      <c r="F133" s="4"/>
+      <c r="G133" s="4"/>
+      <c r="H133" s="4"/>
+      <c r="I133" s="4"/>
+      <c r="J133" s="4"/>
+      <c r="K133" s="4"/>
+      <c r="L133" s="4"/>
+      <c r="M133" s="4"/>
+      <c r="N133" s="4"/>
+      <c r="O133" s="4"/>
+      <c r="P133" s="4"/>
+      <c r="Q133" s="4"/>
+      <c r="R133" s="4"/>
+      <c r="S133" s="4"/>
+      <c r="T133" s="4"/>
+      <c r="U133" s="4"/>
+      <c r="V133" s="4"/>
+      <c r="W133" s="4"/>
+      <c r="X133" s="4"/>
+      <c r="Y133" s="4"/>
+      <c r="Z133" s="4"/>
+      <c r="AA133" s="4"/>
+      <c r="AB133" s="4"/>
+      <c r="AC133" s="4"/>
+      <c r="AD133" s="4"/>
+      <c r="AE133" s="4"/>
+      <c r="AF133" s="4"/>
+      <c r="AG133" s="4"/>
+    </row>
+    <row r="196" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B196" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C196" s="4"/>
+      <c r="D196" s="4"/>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
+      <c r="G196" s="4"/>
+      <c r="H196" s="4"/>
+      <c r="I196" s="4"/>
+      <c r="J196" s="4"/>
+      <c r="K196" s="4"/>
+      <c r="L196" s="4"/>
+      <c r="M196" s="4"/>
+      <c r="N196" s="4"/>
+      <c r="O196" s="4"/>
+      <c r="P196" s="4"/>
+      <c r="Q196" s="4"/>
+      <c r="R196" s="4"/>
+      <c r="S196" s="4"/>
+      <c r="T196" s="4"/>
+      <c r="U196" s="4"/>
+      <c r="V196" s="4"/>
+      <c r="W196" s="4"/>
+      <c r="X196" s="4"/>
+      <c r="Y196" s="4"/>
+      <c r="Z196" s="4"/>
+      <c r="AA196" s="4"/>
+      <c r="AB196" s="4"/>
+      <c r="AC196" s="4"/>
+      <c r="AD196" s="4"/>
+      <c r="AE196" s="4"/>
+      <c r="AF196" s="4"/>
+      <c r="AG196" s="4"/>
+    </row>
+    <row r="231" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B231" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C231" s="4"/>
+      <c r="D231" s="4"/>
+      <c r="E231" s="4"/>
+      <c r="F231" s="4"/>
+      <c r="G231" s="4"/>
+      <c r="H231" s="4"/>
+      <c r="I231" s="4"/>
+      <c r="J231" s="4"/>
+      <c r="K231" s="4"/>
+      <c r="L231" s="4"/>
+      <c r="M231" s="4"/>
+      <c r="N231" s="4"/>
+      <c r="O231" s="4"/>
+      <c r="P231" s="4"/>
+      <c r="Q231" s="4"/>
+      <c r="R231" s="4"/>
+      <c r="S231" s="4"/>
+      <c r="T231" s="4"/>
+      <c r="U231" s="4"/>
+      <c r="V231" s="4"/>
+      <c r="W231" s="4"/>
+      <c r="X231" s="4"/>
+      <c r="Y231" s="4"/>
+      <c r="Z231" s="4"/>
+      <c r="AA231" s="4"/>
+      <c r="AB231" s="4"/>
+      <c r="AC231" s="4"/>
+      <c r="AD231" s="4"/>
+      <c r="AE231" s="4"/>
+      <c r="AF231" s="4"/>
+      <c r="AG231" s="4"/>
+    </row>
+    <row r="294" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B294" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C294" s="4"/>
+      <c r="D294" s="4"/>
+      <c r="E294" s="4"/>
+      <c r="F294" s="4"/>
+      <c r="G294" s="4"/>
+      <c r="H294" s="4"/>
+      <c r="I294" s="4"/>
+      <c r="J294" s="4"/>
+      <c r="K294" s="4"/>
+      <c r="L294" s="4"/>
+      <c r="M294" s="4"/>
+      <c r="N294" s="4"/>
+      <c r="O294" s="4"/>
+      <c r="P294" s="4"/>
+      <c r="Q294" s="4"/>
+      <c r="R294" s="4"/>
+      <c r="S294" s="4"/>
+      <c r="T294" s="4"/>
+      <c r="U294" s="4"/>
+      <c r="V294" s="4"/>
+      <c r="W294" s="4"/>
+      <c r="X294" s="4"/>
+      <c r="Y294" s="4"/>
+      <c r="Z294" s="4"/>
+      <c r="AA294" s="4"/>
+      <c r="AB294" s="4"/>
+      <c r="AC294" s="4"/>
+      <c r="AD294" s="4"/>
+      <c r="AE294" s="4"/>
+      <c r="AF294" s="4"/>
+      <c r="AG294" s="4"/>
+    </row>
+    <row r="357" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B357" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C357" s="4"/>
+      <c r="D357" s="4"/>
+      <c r="E357" s="4"/>
+      <c r="F357" s="4"/>
+      <c r="G357" s="4"/>
+      <c r="H357" s="4"/>
+      <c r="I357" s="4"/>
+      <c r="J357" s="4"/>
+      <c r="K357" s="4"/>
+      <c r="L357" s="4"/>
+      <c r="M357" s="4"/>
+      <c r="N357" s="4"/>
+      <c r="O357" s="4"/>
+      <c r="P357" s="4"/>
+      <c r="Q357" s="4"/>
+      <c r="R357" s="4"/>
+      <c r="S357" s="4"/>
+      <c r="T357" s="4"/>
+      <c r="U357" s="4"/>
+      <c r="V357" s="4"/>
+      <c r="W357" s="4"/>
+      <c r="X357" s="4"/>
+      <c r="Y357" s="4"/>
+      <c r="Z357" s="4"/>
+      <c r="AA357" s="4"/>
+      <c r="AB357" s="4"/>
+      <c r="AC357" s="4"/>
+      <c r="AD357" s="4"/>
+      <c r="AE357" s="4"/>
+      <c r="AF357" s="4"/>
+      <c r="AG357" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="10">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B61:AG61"/>
     <mergeCell ref="B62:AG62"/>
     <mergeCell ref="B97:AG97"/>
-    <mergeCell ref="B160:AG160"/>
-    <mergeCell ref="B195:AG195"/>
-    <mergeCell ref="B258:AG258"/>
+    <mergeCell ref="B98:AG98"/>
+    <mergeCell ref="B133:AG133"/>
+    <mergeCell ref="B196:AG196"/>
+    <mergeCell ref="B231:AG231"/>
+    <mergeCell ref="B294:AG294"/>
+    <mergeCell ref="B357:AG357"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
@@ -2663,7 +2961,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG52"/>
+  <dimension ref="B1:AG61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2672,7 +2970,7 @@
   <sheetData>
     <row r="1" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -2708,10 +3006,10 @@
     </row>
     <row r="2" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
@@ -2722,22 +3020,22 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
       <c r="O2" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P2" s="5"/>
       <c r="Q2" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R2" s="5"/>
       <c r="S2" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -2745,12 +3043,12 @@
       <c r="W2" s="5"/>
       <c r="X2" s="5"/>
       <c r="Y2" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
@@ -2763,33 +3061,33 @@
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
@@ -2797,12 +3095,12 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
       <c r="Y3" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -2815,33 +3113,33 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T4" s="3"/>
       <c r="U4" s="3"/>
@@ -2849,12 +3147,12 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
       <c r="Y4" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
       <c r="AB4" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -2867,33 +3165,33 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R5" s="3"/>
       <c r="S5" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="T5" s="3"/>
       <c r="U5" s="3"/>
@@ -2901,12 +3199,12 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
       <c r="Y5" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
       <c r="AB5" s="3" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -2919,33 +3217,33 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R6" s="3"/>
       <c r="S6" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T6" s="3"/>
       <c r="U6" s="3"/>
@@ -2953,12 +3251,12 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
       <c r="Y6" s="3" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
       <c r="AB6" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -2971,33 +3269,33 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="R7" s="3"/>
       <c r="S7" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T7" s="3"/>
       <c r="U7" s="3"/>
@@ -3005,12 +3303,12 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
       <c r="Y7" s="3" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
       <c r="AB7" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -3023,33 +3321,33 @@
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
       <c r="O8" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R8" s="3"/>
       <c r="S8" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="T8" s="3"/>
       <c r="U8" s="3"/>
@@ -3057,12 +3355,12 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
       <c r="Y8" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
       <c r="AB8" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
@@ -3075,33 +3373,33 @@
         <v>7</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R9" s="3"/>
       <c r="S9" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T9" s="3"/>
       <c r="U9" s="3"/>
@@ -3109,12 +3407,12 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
       <c r="Y9" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
       <c r="AB9" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
@@ -3122,38 +3420,38 @@
       <c r="AF9" s="3"/>
       <c r="AG9" s="3"/>
     </row>
-    <row r="10" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="10" ht="82" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="7">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R10" s="3"/>
       <c r="S10" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T10" s="3"/>
       <c r="U10" s="3"/>
@@ -3161,12 +3459,12 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
       <c r="Y10" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
       <c r="AB10" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
@@ -3179,33 +3477,33 @@
         <v>9</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R11" s="3"/>
       <c r="S11" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
@@ -3213,12 +3511,12 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -3231,33 +3529,33 @@
         <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
@@ -3265,12 +3563,12 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
       <c r="AB12" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -3283,33 +3581,33 @@
         <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P13" s="3"/>
       <c r="Q13" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -3317,12 +3615,12 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
       <c r="AB13" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -3330,38 +3628,38 @@
       <c r="AF13" s="3"/>
       <c r="AG13" s="3"/>
     </row>
-    <row r="14" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="14" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="7">
         <v>12</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -3369,12 +3667,12 @@
       <c r="W14" s="3"/>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
       <c r="AB14" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
@@ -3387,33 +3685,33 @@
         <v>13</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -3421,12 +3719,12 @@
       <c r="W15" s="3"/>
       <c r="X15" s="3"/>
       <c r="Y15" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
       <c r="AB15" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
@@ -3439,33 +3737,33 @@
         <v>14</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
@@ -3473,12 +3771,12 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -3491,33 +3789,33 @@
         <v>15</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R17" s="3"/>
       <c r="S17" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -3525,12 +3823,12 @@
       <c r="W17" s="3"/>
       <c r="X17" s="3"/>
       <c r="Y17" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
       <c r="AB17" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -3543,33 +3841,33 @@
         <v>16</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="R18" s="3"/>
       <c r="S18" s="3" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="T18" s="3"/>
       <c r="U18" s="3"/>
@@ -3577,12 +3875,12 @@
       <c r="W18" s="3"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
       <c r="AB18" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -3595,33 +3893,33 @@
         <v>17</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R19" s="3"/>
       <c r="S19" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
@@ -3629,12 +3927,12 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -3647,33 +3945,33 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="P20" s="3"/>
       <c r="Q20" s="3" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T20" s="3"/>
       <c r="U20" s="3"/>
@@ -3681,12 +3979,12 @@
       <c r="W20" s="3"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
       <c r="AB20" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -3699,33 +3997,33 @@
         <v>19</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="R21" s="3"/>
       <c r="S21" s="3" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="T21" s="3"/>
       <c r="U21" s="3"/>
@@ -3733,12 +4031,12 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
       <c r="Y21" s="3" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
       <c r="AB21" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
@@ -3751,33 +4049,33 @@
         <v>20</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
       <c r="G22" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P22" s="3"/>
       <c r="Q22" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="R22" s="3"/>
       <c r="S22" s="3" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="T22" s="3"/>
       <c r="U22" s="3"/>
@@ -3785,12 +4083,12 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
       <c r="Y22" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
       <c r="AB22" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
@@ -3803,33 +4101,33 @@
         <v>21</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="3" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R23" s="3"/>
       <c r="S23" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T23" s="3"/>
       <c r="U23" s="3"/>
@@ -3837,12 +4135,12 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
       <c r="Y23" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
       <c r="AB23" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -3855,33 +4153,33 @@
         <v>22</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="P24" s="3"/>
       <c r="Q24" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
@@ -3889,12 +4187,12 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
       <c r="Y24" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
       <c r="AB24" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -3907,33 +4205,33 @@
         <v>23</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
       <c r="G25" s="3" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="P25" s="3"/>
       <c r="Q25" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R25" s="3"/>
       <c r="S25" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -3941,12 +4239,12 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
       <c r="Y25" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
       <c r="AB25" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -3959,33 +4257,33 @@
         <v>24</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="P26" s="3"/>
       <c r="Q26" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -3993,12 +4291,12 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
       <c r="Y26" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
       <c r="AB26" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -4011,33 +4309,33 @@
         <v>25</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R27" s="3"/>
       <c r="S27" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -4045,12 +4343,12 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
       <c r="Y27" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
       <c r="AB27" s="3" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -4063,33 +4361,33 @@
         <v>26</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R28" s="3"/>
       <c r="S28" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -4097,12 +4395,12 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
       <c r="AB28" s="3" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -4115,33 +4413,33 @@
         <v>27</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
       <c r="G29" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R29" s="3"/>
       <c r="S29" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
@@ -4149,12 +4447,12 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
       <c r="Y29" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
@@ -4164,7 +4462,7 @@
     </row>
     <row r="31" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4"/>
       <c r="D31" s="4"/>
@@ -4200,10 +4498,10 @@
     </row>
     <row r="32" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D32" s="5"/>
       <c r="E32" s="5"/>
@@ -4214,22 +4512,22 @@
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P32" s="5"/>
       <c r="Q32" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R32" s="5"/>
       <c r="S32" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="T32" s="5"/>
       <c r="U32" s="5"/>
@@ -4237,12 +4535,12 @@
       <c r="W32" s="5"/>
       <c r="X32" s="5"/>
       <c r="Y32" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z32" s="5"/>
       <c r="AA32" s="5"/>
       <c r="AB32" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
@@ -4255,33 +4553,33 @@
         <v>28</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P33" s="3"/>
       <c r="Q33" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R33" s="3"/>
       <c r="S33" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T33" s="3"/>
       <c r="U33" s="3"/>
@@ -4289,12 +4587,12 @@
       <c r="W33" s="3"/>
       <c r="X33" s="3"/>
       <c r="Y33" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
       <c r="AB33" s="3" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
@@ -4304,7 +4602,7 @@
     </row>
     <row r="35" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B35" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" s="4"/>
       <c r="D35" s="4"/>
@@ -4340,10 +4638,10 @@
     </row>
     <row r="36" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -4354,22 +4652,22 @@
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
       <c r="J36" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P36" s="5"/>
       <c r="Q36" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R36" s="5"/>
       <c r="S36" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="T36" s="5"/>
       <c r="U36" s="5"/>
@@ -4377,12 +4675,12 @@
       <c r="W36" s="5"/>
       <c r="X36" s="5"/>
       <c r="Y36" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z36" s="5"/>
       <c r="AA36" s="5"/>
       <c r="AB36" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
@@ -4390,38 +4688,38 @@
       <c r="AF36" s="5"/>
       <c r="AG36" s="5"/>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="37" ht="95" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B37" s="7">
         <v>29</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>86</v>
+        <v>188</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="P37" s="3"/>
       <c r="Q37" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="R37" s="3"/>
       <c r="S37" s="3" t="s">
-        <v>188</v>
+        <v>61</v>
       </c>
       <c r="T37" s="3"/>
       <c r="U37" s="3"/>
@@ -4429,12 +4727,12 @@
       <c r="W37" s="3"/>
       <c r="X37" s="3"/>
       <c r="Y37" s="3" t="s">
-        <v>189</v>
+        <v>61</v>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
       <c r="AB37" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -4442,178 +4740,178 @@
       <c r="AF37" s="3"/>
       <c r="AG37" s="3"/>
     </row>
-    <row r="38" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B38" s="7">
+    <row r="39" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4"/>
+      <c r="V39" s="4"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="4"/>
+      <c r="AA39" s="4"/>
+      <c r="AB39" s="4"/>
+      <c r="AC39" s="4"/>
+      <c r="AD39" s="4"/>
+      <c r="AE39" s="4"/>
+      <c r="AF39" s="4"/>
+      <c r="AG39" s="4"/>
+    </row>
+    <row r="40" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T40" s="5"/>
+      <c r="U40" s="5"/>
+      <c r="V40" s="5"/>
+      <c r="W40" s="5"/>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z40" s="5"/>
+      <c r="AA40" s="5"/>
+      <c r="AB40" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC40" s="5"/>
+      <c r="AD40" s="5"/>
+      <c r="AE40" s="5"/>
+      <c r="AF40" s="5"/>
+      <c r="AG40" s="5"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B41" s="7">
         <v>30</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R38" s="3"/>
-      <c r="S38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z38" s="3"/>
-      <c r="AA38" s="3"/>
-      <c r="AB38" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="AC38" s="3"/>
-      <c r="AD38" s="3"/>
-      <c r="AE38" s="3"/>
-      <c r="AF38" s="3"/>
-      <c r="AG38" s="3"/>
-    </row>
-    <row r="40" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B40" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="4"/>
-      <c r="AC40" s="4"/>
-      <c r="AD40" s="4"/>
-      <c r="AE40" s="4"/>
-      <c r="AF40" s="4"/>
-      <c r="AG40" s="4"/>
-    </row>
-    <row r="41" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="5"/>
-      <c r="O41" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
-      <c r="V41" s="5"/>
-      <c r="W41" s="5"/>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z41" s="5"/>
-      <c r="AA41" s="5"/>
-      <c r="AB41" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC41" s="5"/>
-      <c r="AD41" s="5"/>
-      <c r="AE41" s="5"/>
-      <c r="AF41" s="5"/>
-      <c r="AG41" s="5"/>
-    </row>
-    <row r="42" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P41" s="3"/>
+      <c r="Q41" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+    </row>
+    <row r="42" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B42" s="7">
         <v>31</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R42" s="3"/>
       <c r="S42" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T42" s="3"/>
       <c r="U42" s="3"/>
@@ -4621,12 +4919,12 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
       <c r="Y42" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
       <c r="AB42" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -4636,7 +4934,7 @@
     </row>
     <row r="44" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B44" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -4672,10 +4970,10 @@
     </row>
     <row r="45" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D45" s="5"/>
       <c r="E45" s="5"/>
@@ -4686,22 +4984,22 @@
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
       <c r="J45" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="R45" s="5"/>
       <c r="S45" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="T45" s="5"/>
       <c r="U45" s="5"/>
@@ -4709,12 +5007,12 @@
       <c r="W45" s="5"/>
       <c r="X45" s="5"/>
       <c r="Y45" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="Z45" s="5"/>
       <c r="AA45" s="5"/>
       <c r="AB45" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AC45" s="5"/>
       <c r="AD45" s="5"/>
@@ -4727,33 +5025,33 @@
         <v>32</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
-        <v>54</v>
+        <v>202</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P46" s="3"/>
       <c r="Q46" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="T46" s="3"/>
       <c r="U46" s="3"/>
@@ -4761,12 +5059,12 @@
       <c r="W46" s="3"/>
       <c r="X46" s="3"/>
       <c r="Y46" s="3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
       <c r="AB46" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -4774,252 +5072,584 @@
       <c r="AF46" s="3"/>
       <c r="AG46" s="3"/>
     </row>
-    <row r="47" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B47" s="7">
+    <row r="48" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B48" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="4"/>
+      <c r="AC48" s="4"/>
+      <c r="AD48" s="4"/>
+      <c r="AE48" s="4"/>
+      <c r="AF48" s="4"/>
+      <c r="AG48" s="4"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T49" s="5"/>
+      <c r="U49" s="5"/>
+      <c r="V49" s="5"/>
+      <c r="W49" s="5"/>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z49" s="5"/>
+      <c r="AA49" s="5"/>
+      <c r="AB49" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC49" s="5"/>
+      <c r="AD49" s="5"/>
+      <c r="AE49" s="5"/>
+      <c r="AF49" s="5"/>
+      <c r="AG49" s="5"/>
+    </row>
+    <row r="50" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B50" s="7">
         <v>33</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3" t="s">
+      <c r="C50" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3" t="s">
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+      <c r="M50" s="3"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P50" s="3"/>
+      <c r="Q50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R50" s="3"/>
+      <c r="S50" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T50" s="3"/>
+      <c r="U50" s="3"/>
+      <c r="V50" s="3"/>
+      <c r="W50" s="3"/>
+      <c r="X50" s="3"/>
+      <c r="Y50" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
+      <c r="AB50" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="AC50" s="3"/>
+      <c r="AD50" s="3"/>
+      <c r="AE50" s="3"/>
+      <c r="AF50" s="3"/>
+      <c r="AG50" s="3"/>
+    </row>
+    <row r="51" ht="82" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B51" s="7">
+        <v>34</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K51" s="3"/>
+      <c r="L51" s="3"/>
+      <c r="M51" s="3"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P51" s="3"/>
+      <c r="Q51" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R51" s="3"/>
+      <c r="S51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T51" s="3"/>
+      <c r="U51" s="3"/>
+      <c r="V51" s="3"/>
+      <c r="W51" s="3"/>
+      <c r="X51" s="3"/>
+      <c r="Y51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
+      <c r="AB51" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="AC51" s="3"/>
+      <c r="AD51" s="3"/>
+      <c r="AE51" s="3"/>
+      <c r="AF51" s="3"/>
+      <c r="AG51" s="3"/>
+    </row>
+    <row r="53" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B53" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="4"/>
+      <c r="AD53" s="4"/>
+      <c r="AE53" s="4"/>
+      <c r="AF53" s="4"/>
+      <c r="AG53" s="4"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R54" s="5"/>
+      <c r="S54" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T54" s="5"/>
+      <c r="U54" s="5"/>
+      <c r="V54" s="5"/>
+      <c r="W54" s="5"/>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3" t="s">
+      <c r="Z54" s="5"/>
+      <c r="AA54" s="5"/>
+      <c r="AB54" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3" t="s">
+      <c r="AC54" s="5"/>
+      <c r="AD54" s="5"/>
+      <c r="AE54" s="5"/>
+      <c r="AF54" s="5"/>
+      <c r="AG54" s="5"/>
+    </row>
+    <row r="55" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B55" s="7">
+        <v>35</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+      <c r="AB55" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC55" s="3"/>
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B56" s="7">
+        <v>36</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+      <c r="AB56" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC56" s="3"/>
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B57" s="7">
+        <v>37</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
+      <c r="J57" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K57" s="3"/>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T57" s="3"/>
+      <c r="U57" s="3"/>
+      <c r="V57" s="3"/>
+      <c r="W57" s="3"/>
+      <c r="X57" s="3"/>
+      <c r="Y57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
+      <c r="AB57" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="AC57" s="3"/>
+      <c r="AD57" s="3"/>
+      <c r="AE57" s="3"/>
+      <c r="AF57" s="3"/>
+      <c r="AG57" s="3"/>
+    </row>
+    <row r="59" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B59" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
+      <c r="AB59" s="4"/>
+      <c r="AC59" s="4"/>
+      <c r="AD59" s="4"/>
+      <c r="AE59" s="4"/>
+      <c r="AF59" s="4"/>
+      <c r="AG59" s="4"/>
+    </row>
+    <row r="60" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B60" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="R60" s="5"/>
+      <c r="S60" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="T60" s="5"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5"/>
+      <c r="W60" s="5"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
-      <c r="AB47" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="AC47" s="3"/>
-      <c r="AD47" s="3"/>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="3"/>
-      <c r="AG47" s="3"/>
-    </row>
-    <row r="48" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B48" s="7">
-        <v>34</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-      <c r="J48" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3" t="s">
+      <c r="Z60" s="5"/>
+      <c r="AA60" s="5"/>
+      <c r="AB60" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
-      <c r="AB48" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC48" s="3"/>
-      <c r="AD48" s="3"/>
-      <c r="AE48" s="3"/>
-      <c r="AF48" s="3"/>
-      <c r="AG48" s="3"/>
-    </row>
-    <row r="50" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B50" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AD50" s="4"/>
-      <c r="AE50" s="4"/>
-      <c r="AF50" s="4"/>
-      <c r="AG50" s="4"/>
-    </row>
-    <row r="51" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B51" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="K51" s="5"/>
-      <c r="L51" s="5"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5"/>
-      <c r="O51" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="R51" s="5"/>
-      <c r="S51" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="T51" s="5"/>
-      <c r="U51" s="5"/>
-      <c r="V51" s="5"/>
-      <c r="W51" s="5"/>
-      <c r="X51" s="5"/>
-      <c r="Y51" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z51" s="5"/>
-      <c r="AA51" s="5"/>
-      <c r="AB51" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC51" s="5"/>
-      <c r="AD51" s="5"/>
-      <c r="AE51" s="5"/>
-      <c r="AF51" s="5"/>
-      <c r="AG51" s="5"/>
-    </row>
-    <row r="52" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B52" s="7">
-        <v>35</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-      <c r="J52" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="3"/>
-      <c r="AB52" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="AC52" s="3"/>
-      <c r="AD52" s="3"/>
-      <c r="AE52" s="3"/>
-      <c r="AF52" s="3"/>
-      <c r="AG52" s="3"/>
+      <c r="AC60" s="5"/>
+      <c r="AD60" s="5"/>
+      <c r="AE60" s="5"/>
+      <c r="AF60" s="5"/>
+      <c r="AG60" s="5"/>
+    </row>
+    <row r="61" ht="56" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B61" s="7">
+        <v>38</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="334">
+  <mergeCells count="376">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -5279,15 +5909,15 @@
     <mergeCell ref="S37:X37"/>
     <mergeCell ref="Y37:AA37"/>
     <mergeCell ref="AB37:AG37"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="J38:N38"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="S38:X38"/>
-    <mergeCell ref="Y38:AA38"/>
-    <mergeCell ref="AB38:AG38"/>
-    <mergeCell ref="B40:AG40"/>
+    <mergeCell ref="B39:AG39"/>
+    <mergeCell ref="C40:F40"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="J40:N40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:X40"/>
+    <mergeCell ref="Y40:AA40"/>
+    <mergeCell ref="AB40:AG40"/>
     <mergeCell ref="C41:F41"/>
     <mergeCell ref="G41:I41"/>
     <mergeCell ref="J41:N41"/>
@@ -5321,23 +5951,23 @@
     <mergeCell ref="S46:X46"/>
     <mergeCell ref="Y46:AA46"/>
     <mergeCell ref="AB46:AG46"/>
-    <mergeCell ref="C47:F47"/>
-    <mergeCell ref="G47:I47"/>
-    <mergeCell ref="J47:N47"/>
-    <mergeCell ref="O47:P47"/>
-    <mergeCell ref="Q47:R47"/>
-    <mergeCell ref="S47:X47"/>
-    <mergeCell ref="Y47:AA47"/>
-    <mergeCell ref="AB47:AG47"/>
-    <mergeCell ref="C48:F48"/>
-    <mergeCell ref="G48:I48"/>
-    <mergeCell ref="J48:N48"/>
-    <mergeCell ref="O48:P48"/>
-    <mergeCell ref="Q48:R48"/>
-    <mergeCell ref="S48:X48"/>
-    <mergeCell ref="Y48:AA48"/>
-    <mergeCell ref="AB48:AG48"/>
-    <mergeCell ref="B50:AG50"/>
+    <mergeCell ref="B48:AG48"/>
+    <mergeCell ref="C49:F49"/>
+    <mergeCell ref="G49:I49"/>
+    <mergeCell ref="J49:N49"/>
+    <mergeCell ref="O49:P49"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="S49:X49"/>
+    <mergeCell ref="Y49:AA49"/>
+    <mergeCell ref="AB49:AG49"/>
+    <mergeCell ref="C50:F50"/>
+    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="J50:N50"/>
+    <mergeCell ref="O50:P50"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="S50:X50"/>
+    <mergeCell ref="Y50:AA50"/>
+    <mergeCell ref="AB50:AG50"/>
     <mergeCell ref="C51:F51"/>
     <mergeCell ref="G51:I51"/>
     <mergeCell ref="J51:N51"/>
@@ -5346,14 +5976,56 @@
     <mergeCell ref="S51:X51"/>
     <mergeCell ref="Y51:AA51"/>
     <mergeCell ref="AB51:AG51"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="J52:N52"/>
-    <mergeCell ref="O52:P52"/>
-    <mergeCell ref="Q52:R52"/>
-    <mergeCell ref="S52:X52"/>
-    <mergeCell ref="Y52:AA52"/>
-    <mergeCell ref="AB52:AG52"/>
+    <mergeCell ref="B53:AG53"/>
+    <mergeCell ref="C54:F54"/>
+    <mergeCell ref="G54:I54"/>
+    <mergeCell ref="J54:N54"/>
+    <mergeCell ref="O54:P54"/>
+    <mergeCell ref="Q54:R54"/>
+    <mergeCell ref="S54:X54"/>
+    <mergeCell ref="Y54:AA54"/>
+    <mergeCell ref="AB54:AG54"/>
+    <mergeCell ref="C55:F55"/>
+    <mergeCell ref="G55:I55"/>
+    <mergeCell ref="J55:N55"/>
+    <mergeCell ref="O55:P55"/>
+    <mergeCell ref="Q55:R55"/>
+    <mergeCell ref="S55:X55"/>
+    <mergeCell ref="Y55:AA55"/>
+    <mergeCell ref="AB55:AG55"/>
+    <mergeCell ref="C56:F56"/>
+    <mergeCell ref="G56:I56"/>
+    <mergeCell ref="J56:N56"/>
+    <mergeCell ref="O56:P56"/>
+    <mergeCell ref="Q56:R56"/>
+    <mergeCell ref="S56:X56"/>
+    <mergeCell ref="Y56:AA56"/>
+    <mergeCell ref="AB56:AG56"/>
+    <mergeCell ref="C57:F57"/>
+    <mergeCell ref="G57:I57"/>
+    <mergeCell ref="J57:N57"/>
+    <mergeCell ref="O57:P57"/>
+    <mergeCell ref="Q57:R57"/>
+    <mergeCell ref="S57:X57"/>
+    <mergeCell ref="Y57:AA57"/>
+    <mergeCell ref="AB57:AG57"/>
+    <mergeCell ref="B59:AG59"/>
+    <mergeCell ref="C60:F60"/>
+    <mergeCell ref="G60:I60"/>
+    <mergeCell ref="J60:N60"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="S60:X60"/>
+    <mergeCell ref="Y60:AA60"/>
+    <mergeCell ref="AB60:AG60"/>
+    <mergeCell ref="C61:F61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:N61"/>
+    <mergeCell ref="O61:P61"/>
+    <mergeCell ref="Q61:R61"/>
+    <mergeCell ref="S61:X61"/>
+    <mergeCell ref="Y61:AA61"/>
+    <mergeCell ref="AB61:AG61"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
@@ -5364,7 +6036,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:AG41"/>
+  <dimension ref="B1:AG44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -5373,7 +6045,7 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -5409,7 +6081,7 @@
     </row>
     <row r="2" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
@@ -5445,10 +6117,10 @@
     </row>
     <row r="3" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B3" s="8" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -5483,10 +6155,10 @@
     </row>
     <row r="4" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B4" s="8" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
@@ -5521,10 +6193,10 @@
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B5" s="8" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -5559,10 +6231,10 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="D6" s="6"/>
       <c r="E6" s="6"/>
@@ -5597,7 +6269,7 @@
     </row>
     <row r="8" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -5633,10 +6305,10 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B9" s="8" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -5671,10 +6343,10 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
@@ -5709,10 +6381,10 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B11" s="8" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -5747,13 +6419,13 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
       <c r="F12" s="5" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
@@ -5768,7 +6440,7 @@
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
       <c r="S12" s="5" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
@@ -5785,15 +6457,15 @@
       <c r="AF12" s="5"/>
       <c r="AG12" s="5"/>
     </row>
-    <row r="13" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="13" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
@@ -5808,7 +6480,7 @@
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
       <c r="S13" s="3" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -5827,13 +6499,13 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -5848,7 +6520,7 @@
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
       <c r="S14" s="3" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="T14" s="3"/>
       <c r="U14" s="3"/>
@@ -5867,13 +6539,13 @@
     </row>
     <row r="15" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -5888,7 +6560,7 @@
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
       <c r="S15" s="3" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="T15" s="3"/>
       <c r="U15" s="3"/>
@@ -5907,7 +6579,7 @@
     </row>
     <row r="16" ht="43" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -5943,7 +6615,7 @@
     </row>
     <row r="18" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B18" s="4" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -5979,10 +6651,10 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B19" s="8" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -6017,10 +6689,10 @@
     </row>
     <row r="20" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B20" s="8" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -6055,10 +6727,10 @@
     </row>
     <row r="21" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B21" s="8" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -6093,10 +6765,10 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B22" s="8" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -6131,7 +6803,7 @@
     </row>
     <row r="24" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B24" s="4" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -6167,7 +6839,7 @@
     </row>
     <row r="25" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -6181,11 +6853,11 @@
       <c r="L25" s="5"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="O25" s="5"/>
       <c r="P25" s="5" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
@@ -6207,7 +6879,7 @@
     </row>
     <row r="26" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B26" s="3" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
@@ -6221,11 +6893,11 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="O26" s="3"/>
       <c r="P26" s="3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="Q26" s="3"/>
       <c r="R26" s="3"/>
@@ -6247,7 +6919,7 @@
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -6265,7 +6937,7 @@
       </c>
       <c r="O27" s="7"/>
       <c r="P27" s="3" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
@@ -6287,7 +6959,7 @@
     </row>
     <row r="28" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -6300,12 +6972,12 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
-      <c r="N28" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="O28" s="3"/>
+      <c r="N28" s="7">
+        <v>409</v>
+      </c>
+      <c r="O28" s="7"/>
       <c r="P28" s="3" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="Q28" s="3"/>
       <c r="R28" s="3"/>
@@ -6325,9 +6997,9 @@
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
     </row>
-    <row r="29" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -6341,11 +7013,11 @@
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="Q29" s="3"/>
       <c r="R29" s="3"/>
@@ -6367,7 +7039,7 @@
     </row>
     <row r="30" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B30" s="3" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -6385,7 +7057,7 @@
       </c>
       <c r="O30" s="7"/>
       <c r="P30" s="3" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="Q30" s="3"/>
       <c r="R30" s="3"/>
@@ -6405,9 +7077,9 @@
       <c r="AF30" s="3"/>
       <c r="AG30" s="3"/>
     </row>
-    <row r="31" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="31" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B31" s="3" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -6420,12 +7092,12 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
-      <c r="N31" s="7">
-        <v>400</v>
-      </c>
-      <c r="O31" s="7"/>
+      <c r="N31" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="O31" s="3"/>
       <c r="P31" s="3" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -6445,9 +7117,9 @@
       <c r="AF31" s="3"/>
       <c r="AG31" s="3"/>
     </row>
-    <row r="32" spans="2:33" x14ac:dyDescent="0.25">
+    <row r="32" ht="30" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B32" s="3" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -6460,12 +7132,12 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
-      <c r="N32" s="7">
-        <v>400</v>
-      </c>
-      <c r="O32" s="7"/>
+      <c r="N32" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="O32" s="3"/>
       <c r="P32" s="3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="Q32" s="3"/>
       <c r="R32" s="3"/>
@@ -6487,7 +7159,7 @@
     </row>
     <row r="33" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -6505,7 +7177,7 @@
       </c>
       <c r="O33" s="7"/>
       <c r="P33" s="3" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="Q33" s="3"/>
       <c r="R33" s="3"/>
@@ -6527,7 +7199,7 @@
     </row>
     <row r="34" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -6545,7 +7217,7 @@
       </c>
       <c r="O34" s="7"/>
       <c r="P34" s="3" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="Q34" s="3"/>
       <c r="R34" s="3"/>
@@ -6567,7 +7239,7 @@
     </row>
     <row r="35" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -6585,7 +7257,7 @@
       </c>
       <c r="O35" s="7"/>
       <c r="P35" s="3" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="Q35" s="3"/>
       <c r="R35" s="3"/>
@@ -6607,7 +7279,7 @@
     </row>
     <row r="36" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B36" s="3" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
@@ -6621,11 +7293,11 @@
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
       <c r="N36" s="7">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="O36" s="7"/>
       <c r="P36" s="3" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="Q36" s="3"/>
       <c r="R36" s="3"/>
@@ -6647,7 +7319,7 @@
     </row>
     <row r="37" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B37" s="3" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -6665,7 +7337,7 @@
       </c>
       <c r="O37" s="7"/>
       <c r="P37" s="3" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="Q37" s="3"/>
       <c r="R37" s="3"/>
@@ -6687,7 +7359,7 @@
     </row>
     <row r="38" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B38" s="3" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -6705,7 +7377,7 @@
       </c>
       <c r="O38" s="7"/>
       <c r="P38" s="3" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="Q38" s="3"/>
       <c r="R38" s="3"/>
@@ -6727,7 +7399,7 @@
     </row>
     <row r="39" spans="2:33" x14ac:dyDescent="0.25">
       <c r="B39" s="3" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -6740,12 +7412,12 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-      <c r="N39" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="O39" s="3"/>
+      <c r="N39" s="7">
+        <v>403</v>
+      </c>
+      <c r="O39" s="7"/>
       <c r="P39" s="3" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
@@ -6765,44 +7437,164 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
     </row>
-    <row r="41" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
-      <c r="B41" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
-      <c r="AB41" s="4"/>
-      <c r="AC41" s="4"/>
-      <c r="AD41" s="4"/>
-      <c r="AE41" s="4"/>
-      <c r="AF41" s="4"/>
-      <c r="AG41" s="4"/>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
+      <c r="L40" s="3"/>
+      <c r="M40" s="3"/>
+      <c r="N40" s="7">
+        <v>400</v>
+      </c>
+      <c r="O40" s="7"/>
+      <c r="P40" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B41" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="3"/>
+      <c r="M41" s="3"/>
+      <c r="N41" s="7">
+        <v>400</v>
+      </c>
+      <c r="O41" s="7"/>
+      <c r="P41" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="Q41" s="3"/>
+      <c r="R41" s="3"/>
+      <c r="S41" s="3"/>
+      <c r="T41" s="3"/>
+      <c r="U41" s="3"/>
+      <c r="V41" s="3"/>
+      <c r="W41" s="3"/>
+      <c r="X41" s="3"/>
+      <c r="Y41" s="3"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
+      <c r="AB41" s="3"/>
+      <c r="AC41" s="3"/>
+      <c r="AD41" s="3"/>
+      <c r="AE41" s="3"/>
+      <c r="AF41" s="3"/>
+      <c r="AG41" s="3"/>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+      <c r="M42" s="3"/>
+      <c r="N42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="3"/>
+      <c r="S42" s="3"/>
+      <c r="T42" s="3"/>
+      <c r="U42" s="3"/>
+      <c r="V42" s="3"/>
+      <c r="W42" s="3"/>
+      <c r="X42" s="3"/>
+      <c r="Y42" s="3"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
+      <c r="AB42" s="3"/>
+      <c r="AC42" s="3"/>
+      <c r="AD42" s="3"/>
+      <c r="AE42" s="3"/>
+      <c r="AF42" s="3"/>
+      <c r="AG42" s="3"/>
+    </row>
+    <row r="44" ht="21" customHeight="1" spans="2:33" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
+      <c r="P44" s="4"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+      <c r="AC44" s="4"/>
+      <c r="AD44" s="4"/>
+      <c r="AE44" s="4"/>
+      <c r="AF44" s="4"/>
+      <c r="AG44" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="75">
+  <mergeCells count="84">
     <mergeCell ref="B1:AG1"/>
     <mergeCell ref="B2:AG2"/>
     <mergeCell ref="C3:AG3"/>
@@ -6877,7 +7669,16 @@
     <mergeCell ref="B39:M39"/>
     <mergeCell ref="N39:O39"/>
     <mergeCell ref="P39:AG39"/>
-    <mergeCell ref="B41:AG41"/>
+    <mergeCell ref="B40:M40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="P40:AG40"/>
+    <mergeCell ref="B41:M41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="P41:AG41"/>
+    <mergeCell ref="B42:M42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="P42:AG42"/>
+    <mergeCell ref="B44:AG44"/>
   </mergeCells>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
